--- a/SW제품 테스트 결과보고서_작성본.xlsx
+++ b/SW제품 테스트 결과보고서_작성본.xlsx
@@ -1201,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.88671875" customWidth="1" style="11" min="1" max="1"/>
@@ -1766,24 +1766,20 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>직전 입력값이 남아있음(초기화 안 됨)</t>
+          <t>D3 단독세션 재검증 시 취소/재오픈 모두 정상 초기화 확인(D1 대비 수정됨)</t>
         </is>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t>경미</t>
-        </is>
-      </c>
-      <c r="J13" s="34" t="inlineStr">
-        <is>
-          <t>E-007</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="34" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n">
@@ -2198,7 +2194,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에디터가 white screen으로 크래시(새로고침 필요). 간헐 발생</t>
+          <t>초기 1회 white screen 크래시 목격. D3 배치 업로드 33회+ 재시도에도 미재현(재현조건 미확정). ※배치에 미지원 포맷 포함 시 데이터 손실은 E-018로 별도 확정</t>
         </is>
       </c>
       <c r="H22" s="26" t="inlineStr">
@@ -2208,7 +2204,7 @@
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
-          <t>심각</t>
+          <t>경미(간헐·재현불가)</t>
         </is>
       </c>
       <c r="J22" s="34" t="inlineStr">
@@ -2874,24 +2870,20 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>2회 클릭해도 아무 반응·안내 없음</t>
+          <t>D3 재검증 시 '주소가 복사되었습니다' 토스트 정상 표시(D1 대비 수정됨)</t>
         </is>
       </c>
       <c r="H36" s="26" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I36" s="26" t="inlineStr">
         <is>
-          <t>경미</t>
-        </is>
-      </c>
-      <c r="J36" s="34" t="inlineStr">
-        <is>
-          <t>E-006</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="34" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="34" t="n">
@@ -3039,12 +3031,315 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="48" customHeight="1" s="47">
+      <c r="A40" s="34" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>360이미지</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>업로드</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>배치 업로드 무결성</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>1. 정상 파일 + 미지원 포맷(webp/gif) 1장을 함께 다중선택하여 1회 업로드
+2. 통제비교: (a)정상만 (b)정상+해상도실패 (c)정상+포맷거부 배치 각각 결과 확인</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>미지원 파일만 개별 실패하고 정상 파일은 정상 등록(부분 성공)</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>배치에 미지원 포맷(webp/gif=빈 jobId) 1장만 있어도 정상 파일까지 전량 등록 실패(데이터 손실). 해상도실패만 있는 배치는 정상분 생존→포맷거부가 배치 커밋을 롤백. 재현 100%(거부단독·최소재현·10/12장), 실패 사유 안내 없음+빈 유령 카테고리 생성</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="J40" s="34" t="inlineStr">
+        <is>
+          <t>E-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" s="47">
+      <c r="A41" s="34" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>360이미지</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>업로드</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>특정 해상도 처리 실패</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1. 정상 2:1 파노라마를 해상도만 달리하여 업로드(7180×3590 / 10771×5385 / 11968×5984)
+2. 동일 콘텐츠로 해상도만 스왑(통제실험)</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>정상 규격(2:1·유효 JPEG·적정 용량) 파노라마는 해상도와 무관하게 등록</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>≈1만×5천(10771×5385 등) 해상도는 처리 실패(jobId 발급 후 씬 미등록), 7180×3590·11968×5984는 통과. 콘텐츠 고정·해상도만 스왑 시 성패 반전→해상도가 유일 원인(용량·비율·홀짝 반증). 실패 사유·허용범위 안내 없음</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J41" s="34" t="inlineStr">
+        <is>
+          <t>E-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" s="47">
+      <c r="A42" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>360이미지</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>업로드</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>지원 포맷 정책 불일치</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>1. 통과 해상도(7180×3590)로 jpg/png/webp/gif 각각 업로드
+2. 파일선택창 input accept 속성 확인</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>선택 가능한 포맷은 실제 처리되거나, 불가 포맷은 선택 단계에서 제한</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>씬 업로드 input은 accept='image/*'로 webp/gif 선택 허용하나 서버는 jpeg/png만 처리(webp/gif 거부). 같은 앱 다른 업로드 input은 accept='image/png,image/jpeg'로 제한→입력 간 정책 불일치</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>경미</t>
+        </is>
+      </c>
+      <c r="J42" s="34" t="inlineStr">
+        <is>
+          <t>E-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" s="47">
+      <c r="A43" s="34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>핫스팟</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>핫스팟 수정</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1. 생성된 핫스팟의 제목/위치 수정 시도</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>생성된 핫스팟을 편집(제목·위치 등) 가능</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>'핫스팟은 수정할 수 없습니다. 새로 등록해주세요' — 수정 기능 부재, 삭제 후 재등록만 가능</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="J43" s="34" t="inlineStr">
+        <is>
+          <t>E-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1" s="47">
+      <c r="A44" s="34" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>회사</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>회사 관리</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>이메일 형식 검증</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>1. 회사 수정 &gt; 이메일에 '@' 없는 문자열(invalidemail) 입력 &gt; 저장</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>이메일 형식 검증으로 저장 차단·안내</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>형식 검증 없이 '@' 없는 값도 저장됨('수정이 완료 되었습니다')</t>
+        </is>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>경미</t>
+        </is>
+      </c>
+      <c r="J44" s="34" t="inlineStr">
+        <is>
+          <t>E-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" s="47">
+      <c r="A45" s="34" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>핫스팟</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>삭제 다이얼로그 현지화</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>1. 핫스팟 삭제 클릭 &gt; 확인 다이얼로그/토스트 언어 확인</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>앱 전체(한글)와 일관된 한글 표기</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>핫스팟 삭제만 영문(Delete this hotspot / Delete / Cancel, 토스트 'Delete successfully.')</t>
+        </is>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>경미</t>
+        </is>
+      </c>
+      <c r="J45" s="34" t="inlineStr">
+        <is>
+          <t>E-023</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
   </mergeCells>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="landscape" paperSize="9" scale="56" fitToHeight="0"/>
@@ -3057,7 +3352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.6640625" customWidth="1" style="19" min="1" max="1"/>
@@ -3260,6 +3555,78 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>E-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>E-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>E-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>E-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>E-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>E-023</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K2:K10"/>
